--- a/artfynd/A 15918-2024 artfynd.xlsx
+++ b/artfynd/A 15918-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117453300</v>
+        <v>117453463</v>
       </c>
       <c r="B3" t="n">
-        <v>56499</v>
+        <v>97836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516924</v>
+        <v>517068</v>
       </c>
       <c r="R3" t="n">
-        <v>6691616</v>
+        <v>6691652</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117453463</v>
+        <v>117453300</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>56499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517068</v>
+        <v>516924</v>
       </c>
       <c r="R4" t="n">
-        <v>6691652</v>
+        <v>6691616</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 15918-2024 artfynd.xlsx
+++ b/artfynd/A 15918-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>117453463</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>117453300</v>
       </c>
       <c r="B4" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>117452633</v>
       </c>
       <c r="B5" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
